--- a/FastReact Confg..xlsx
+++ b/FastReact Confg..xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. Work\1. Daily\Capacity Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC51413C-8D5D-4C49-809B-204983A5B546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F83E07-8D07-4D4A-B6F6-9741F9826CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{9AFED8FC-535D-48D6-A46B-931961F691BE}"/>
   </bookViews>
@@ -625,10 +625,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D3" s="8">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>7</v>
@@ -642,10 +642,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="8">
-        <v>46054</v>
+        <v>46113</v>
       </c>
       <c r="D4" s="8">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>30</v>
@@ -659,10 +659,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="8">
-        <v>46054</v>
+        <v>46113</v>
       </c>
       <c r="D5" s="8">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>33</v>
@@ -676,10 +676,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D6" s="8">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>7</v>
@@ -693,10 +693,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D7" s="8">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>7</v>
@@ -710,10 +710,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D8" s="8">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>18</v>
@@ -727,10 +727,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D9" s="8">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>21</v>
@@ -744,10 +744,10 @@
         <v>23</v>
       </c>
       <c r="C10" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D10" s="8">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>21</v>
@@ -761,10 +761,10 @@
         <v>24</v>
       </c>
       <c r="C11" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D11" s="8">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>18</v>
@@ -778,10 +778,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D12" s="8">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>18</v>
@@ -795,10 +795,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D13" s="8">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>18</v>
@@ -812,10 +812,10 @@
         <v>32</v>
       </c>
       <c r="C14" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D14" s="8">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>21</v>
@@ -829,10 +829,10 @@
         <v>35</v>
       </c>
       <c r="C15" s="8">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D15" s="8">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>21</v>

--- a/FastReact Confg..xlsx
+++ b/FastReact Confg..xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. Work\1. Daily\Capacity Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F83E07-8D07-4D4A-B6F6-9741F9826CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0984D2CA-FEE9-4EC0-A258-C79349632CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{9AFED8FC-535D-48D6-A46B-931961F691BE}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>Report Name</t>
   </si>
@@ -108,24 +108,6 @@
     <t>Reports- Planning- Buyer wise plan qty- Per_Day_Requirement (Unit)</t>
   </si>
   <si>
-    <t>Reports- Auto status- Buyer Wise Monthly print Req- Buyer Wise Monthly print Req.</t>
-  </si>
-  <si>
-    <t>Reports- Auto status- Buyer Wise Monthly Emb Req- Buyer Wise Monthly Emb Req.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BuyerWise Monthly Wash Req  </t>
-  </si>
-  <si>
-    <t>Reports- Auto status- Buyer Wise Monthly Wash Req- Buyer Wise Monthly Wash Req.</t>
-  </si>
-  <si>
-    <t>BuyerWise Monthly Emb Req</t>
-  </si>
-  <si>
-    <t>BuyerWise Monthly Print Req.</t>
-  </si>
-  <si>
     <t>Current Month + 5</t>
   </si>
   <si>
@@ -145,6 +127,12 @@
   </si>
   <si>
     <t>FastReact planning necessary report configurations</t>
+  </si>
+  <si>
+    <t>Unit wise Detail Plan</t>
+  </si>
+  <si>
+    <t>Reports-Production-UNITWISE DETAIL LINE PLAN-JFL Detail Plan</t>
   </si>
 </sst>
 </file>
@@ -580,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293FE00B-EC13-46E8-B78F-2F1EC25697CE}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.28515625" style="2" customWidth="1"/>
@@ -593,7 +581,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -625,10 +613,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="8">
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="D3" s="8">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>7</v>
@@ -642,13 +630,13 @@
         <v>9</v>
       </c>
       <c r="C4" s="8">
-        <v>46113</v>
+        <v>46204</v>
       </c>
       <c r="D4" s="8">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -659,13 +647,13 @@
         <v>11</v>
       </c>
       <c r="C5" s="8">
-        <v>46113</v>
+        <v>46204</v>
       </c>
       <c r="D5" s="8">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -676,10 +664,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="8">
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="D6" s="8">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>7</v>
@@ -693,10 +681,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="8">
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="D7" s="8">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>7</v>
@@ -710,10 +698,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="8">
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="D8" s="8">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>18</v>
@@ -727,10 +715,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="8">
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="D9" s="8">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>21</v>
@@ -744,97 +732,63 @@
         <v>23</v>
       </c>
       <c r="C10" s="8">
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="D10" s="8">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="8">
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="D11" s="8">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C12" s="8">
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="D12" s="8">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C13" s="8">
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="D13" s="8">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="8">
-        <v>46143</v>
-      </c>
-      <c r="D14" s="8">
-        <v>46173</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="8">
-        <v>46143</v>
-      </c>
-      <c r="D15" s="8">
-        <v>46173</v>
-      </c>
-      <c r="E15" s="9" t="s">
         <v>21</v>
       </c>
     </row>

--- a/FastReact Confg..xlsx
+++ b/FastReact Confg..xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. Work\1. Daily\Capacity Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0984D2CA-FEE9-4EC0-A258-C79349632CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E0DC10-BE70-4FB1-9851-25C8C0EC716D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{9AFED8FC-535D-48D6-A46B-931961F691BE}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Report Name</t>
   </si>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>Reports-Production-UNITWISE DETAIL LINE PLAN-JFL Detail Plan</t>
+  </si>
+  <si>
+    <t>Blank Days Per Month</t>
+  </si>
+  <si>
+    <t>JFL Monthly</t>
   </si>
 </sst>
 </file>
@@ -568,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293FE00B-EC13-46E8-B78F-2F1EC25697CE}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.28515625" style="2" customWidth="1"/>
@@ -613,10 +619,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="8">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="D3" s="8">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>7</v>
@@ -630,10 +636,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="8">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="D4" s="8">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>24</v>
@@ -647,10 +653,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="8">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="D5" s="8">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>27</v>
@@ -664,10 +670,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="8">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="D6" s="8">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>7</v>
@@ -681,10 +687,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="8">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="D7" s="8">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>7</v>
@@ -698,10 +704,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="8">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="D8" s="8">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>18</v>
@@ -715,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="8">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="D9" s="8">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>21</v>
@@ -732,10 +738,10 @@
         <v>23</v>
       </c>
       <c r="C10" s="8">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="D10" s="8">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>21</v>
@@ -749,10 +755,10 @@
         <v>26</v>
       </c>
       <c r="C11" s="8">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="D11" s="8">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>21</v>
@@ -766,10 +772,10 @@
         <v>29</v>
       </c>
       <c r="C12" s="8">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="D12" s="8">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>21</v>
@@ -783,12 +789,29 @@
         <v>32</v>
       </c>
       <c r="C13" s="8">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="D13" s="8">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="E13" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="8">
+        <v>46266</v>
+      </c>
+      <c r="D14" s="8">
+        <v>46295</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>21</v>
       </c>
     </row>
